--- a/Design/Excel/ET/Datas/AIConfig.xlsx
+++ b/Design/Excel/ET/Datas/AIConfig.xlsx
@@ -1047,245 +1047,190 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="9.60833333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.8583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" ht="16.5" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:6">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4">
-        <v>101</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:6">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4">
-        <v>102</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:H5"/>
+  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
+  <ns0:cols>
+    <ns0:col min="1" max="2" width="9" style="1"/>
+    <ns0:col min="3" max="3" width="9.60833333333333" style="1" customWidth="1"/>
+    <ns0:col min="4" max="4" width="11.625" style="1" customWidth="1"/>
+    <ns0:col min="5" max="5" width="15.8583333333333" style="1" customWidth="1"/>
+    <ns0:col min="6" max="6" width="23.875" style="1" customWidth="1"/>
+    <ns0:col min="7" max="7" width="9.25" style="1" customWidth="1"/>
+    <ns0:col min="8" max="8" width="14.375" style="1" customWidth="1"/>
+    <ns0:col min="9" max="16384" width="9" style="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" ht="16.5" spans="1:8">
+      <ns0:c r="A1" s="2" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="3" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="3" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="3" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="3" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="3" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="3" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" s="4"/>
+    </ns0:row>
+    <ns0:row r="2" ht="16.5" spans="1:7">
+      <ns0:c r="A2" s="2" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="3" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="3" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="3" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="3" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="3" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="3" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" ht="16.5" spans="1:7">
+      <ns0:c r="A3" s="2" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="3" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="3" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="3" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="3" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="3" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="3" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:headerFooter/>
+</ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="9.60833333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.8583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" ht="16.5" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:6">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4">
-        <f>C4*100+D4</f>
-        <v>201</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:2">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:H5"/>
+  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
+  <ns0:cols>
+    <ns0:col min="1" max="2" width="9" style="1"/>
+    <ns0:col min="3" max="3" width="9.60833333333333" style="1" customWidth="1"/>
+    <ns0:col min="4" max="4" width="11.625" style="1" customWidth="1"/>
+    <ns0:col min="5" max="5" width="15.8583333333333" style="1" customWidth="1"/>
+    <ns0:col min="6" max="6" width="14.625" style="1" customWidth="1"/>
+    <ns0:col min="7" max="7" width="30.5" style="1" customWidth="1"/>
+    <ns0:col min="8" max="8" width="14.375" style="1" customWidth="1"/>
+    <ns0:col min="9" max="16384" width="9" style="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" ht="16.5" spans="1:8">
+      <ns0:c r="A1" s="2" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="3" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="3" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="3" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="3" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="3" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="3" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" s="4"/>
+    </ns0:row>
+    <ns0:row r="2" ht="16.5" spans="1:8">
+      <ns0:c r="A2" s="2" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="3" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="3" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="3" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="3" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="3" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="3" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" s="4"/>
+    </ns0:row>
+    <ns0:row r="3" ht="16.5" spans="1:7">
+      <ns0:c r="A3" s="2" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="3" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="3" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="3" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="3" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="3" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="3" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5" ht="16.5" spans="1:2">
+      <ns0:c r="A5" s="4"/>
+      <ns0:c r="B5" s="4"/>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:headerFooter/>
+</ns0:worksheet>
 </file>